--- a/testdata/generated_employee_details.xlsx
+++ b/testdata/generated_employee_details.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ATZG57</v>
+        <v>ATVC00</v>
       </c>
       <c r="B2" t="str">
-        <v>Dawn</v>
+        <v>Brandy</v>
       </c>
       <c r="C2" t="str">
-        <v>Herman</v>
+        <v>Wiegand</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,13 +481,13 @@
         <v>8976589760</v>
       </c>
       <c r="F2" t="str">
-        <v>Eddie72@gmail.com</v>
+        <v>Alicia_Monahan@yahoo.com</v>
       </c>
       <c r="G2" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-20</v>
       </c>
       <c r="I2" t="str">
         <v>B.Tech</v>
@@ -531,13 +531,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ASSW69</v>
+        <v>ACUA75</v>
       </c>
       <c r="B3" t="str">
-        <v>Carleton</v>
+        <v>Patsy</v>
       </c>
       <c r="C3" t="str">
-        <v>Howe</v>
+        <v>Langworth</v>
       </c>
       <c r="D3" t="str">
         <v>Male</v>
@@ -546,13 +546,13 @@
         <v>8976589760</v>
       </c>
       <c r="F3" t="str">
-        <v>Lloyd_Mayer93@gmail.com</v>
+        <v>Karl80@hotmail.com</v>
       </c>
       <c r="G3" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-23</v>
       </c>
       <c r="I3" t="str">
         <v>B.Tech</v>
@@ -596,13 +596,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AEFX98</v>
+        <v>AYGK27</v>
       </c>
       <c r="B4" t="str">
-        <v>Elmo</v>
+        <v>Miracle</v>
       </c>
       <c r="C4" t="str">
-        <v>Kutch</v>
+        <v>Adams</v>
       </c>
       <c r="D4" t="str">
         <v>Male</v>
@@ -611,13 +611,13 @@
         <v>8976589760</v>
       </c>
       <c r="F4" t="str">
-        <v>Felipe.Shields98@yahoo.com</v>
+        <v>Miller90@gmail.com</v>
       </c>
       <c r="G4" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-24</v>
       </c>
       <c r="I4" t="str">
         <v>B.Tech</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ANVJ86</v>
+        <v>AVYZ74</v>
       </c>
       <c r="B5" t="str">
-        <v>Ruben</v>
+        <v>Wm</v>
       </c>
       <c r="C5" t="str">
-        <v>Nolan</v>
+        <v>Zemlak</v>
       </c>
       <c r="D5" t="str">
         <v>Male</v>
@@ -676,13 +676,13 @@
         <v>8976589760</v>
       </c>
       <c r="F5" t="str">
-        <v>Isac_Jacobson90@gmail.com</v>
+        <v>Christy.Toy@yahoo.com</v>
       </c>
       <c r="G5" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-25</v>
       </c>
       <c r="I5" t="str">
         <v>B.Tech</v>
@@ -726,13 +726,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AZEG21</v>
+        <v>AYEG55</v>
       </c>
       <c r="B6" t="str">
-        <v>Damian</v>
+        <v>Josh</v>
       </c>
       <c r="C6" t="str">
-        <v>Kemmer</v>
+        <v>Rempel</v>
       </c>
       <c r="D6" t="str">
         <v>Male</v>
@@ -741,13 +741,13 @@
         <v>8976589760</v>
       </c>
       <c r="F6" t="str">
-        <v>Karelle_Lueilwitz@hotmail.com</v>
+        <v>Mary3@yahoo.com</v>
       </c>
       <c r="G6" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-26</v>
       </c>
       <c r="I6" t="str">
         <v>B.Tech</v>

--- a/testdata/generated_employee_details.xlsx
+++ b/testdata/generated_employee_details.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ATVC00</v>
+        <v>AXHU47</v>
       </c>
       <c r="B2" t="str">
-        <v>Brandy</v>
+        <v>Alyssa</v>
       </c>
       <c r="C2" t="str">
-        <v>Wiegand</v>
+        <v>Bergnaum</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,13 +481,13 @@
         <v>8976589760</v>
       </c>
       <c r="F2" t="str">
-        <v>Alicia_Monahan@yahoo.com</v>
+        <v>Kyle.Balistreri@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="I2" t="str">
         <v>B.Tech</v>
@@ -531,13 +531,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ACUA75</v>
+        <v>ANEP87</v>
       </c>
       <c r="B3" t="str">
-        <v>Patsy</v>
+        <v>Velva</v>
       </c>
       <c r="C3" t="str">
-        <v>Langworth</v>
+        <v>Reichel</v>
       </c>
       <c r="D3" t="str">
         <v>Male</v>
@@ -546,7 +546,7 @@
         <v>8976589760</v>
       </c>
       <c r="F3" t="str">
-        <v>Karl80@hotmail.com</v>
+        <v>Stanley_Ryan-Ortiz6@hotmail.com</v>
       </c>
       <c r="G3" t="str">
         <v>2003-02-09</v>
@@ -596,13 +596,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AYGK27</v>
+        <v>AMFH72</v>
       </c>
       <c r="B4" t="str">
-        <v>Miracle</v>
+        <v>Eleanora</v>
       </c>
       <c r="C4" t="str">
-        <v>Adams</v>
+        <v>Muller</v>
       </c>
       <c r="D4" t="str">
         <v>Male</v>
@@ -611,7 +611,7 @@
         <v>8976589760</v>
       </c>
       <c r="F4" t="str">
-        <v>Miller90@gmail.com</v>
+        <v>Mitchell53@hotmail.com</v>
       </c>
       <c r="G4" t="str">
         <v>2003-02-09</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AVYZ74</v>
+        <v>AEBZ21</v>
       </c>
       <c r="B5" t="str">
-        <v>Wm</v>
+        <v>Walter</v>
       </c>
       <c r="C5" t="str">
-        <v>Zemlak</v>
+        <v>Gutmann</v>
       </c>
       <c r="D5" t="str">
         <v>Male</v>
@@ -676,7 +676,7 @@
         <v>8976589760</v>
       </c>
       <c r="F5" t="str">
-        <v>Christy.Toy@yahoo.com</v>
+        <v>Ena_Murphy83@gmail.com</v>
       </c>
       <c r="G5" t="str">
         <v>2003-02-09</v>
@@ -726,13 +726,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AYEG55</v>
+        <v>APQV48</v>
       </c>
       <c r="B6" t="str">
-        <v>Josh</v>
+        <v>Irma</v>
       </c>
       <c r="C6" t="str">
-        <v>Rempel</v>
+        <v>Okuneva</v>
       </c>
       <c r="D6" t="str">
         <v>Male</v>
@@ -741,7 +741,7 @@
         <v>8976589760</v>
       </c>
       <c r="F6" t="str">
-        <v>Mary3@yahoo.com</v>
+        <v>Bobbie_Gleichner68@gmail.com</v>
       </c>
       <c r="G6" t="str">
         <v>2003-02-09</v>

--- a/testdata/generated_employee_details.xlsx
+++ b/testdata/generated_employee_details.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AXHU47</v>
+        <v>AZLI45</v>
       </c>
       <c r="B2" t="str">
-        <v>Alyssa</v>
+        <v>Elsa</v>
       </c>
       <c r="C2" t="str">
-        <v>Bergnaum</v>
+        <v>Crist</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>8976589760</v>
       </c>
       <c r="F2" t="str">
-        <v>Kyle.Balistreri@gmail.com</v>
+        <v>Jeremiah_Auer1@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>2003-02-09</v>
@@ -531,13 +531,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ANEP87</v>
+        <v>AJRM91</v>
       </c>
       <c r="B3" t="str">
-        <v>Velva</v>
+        <v>Deshaun</v>
       </c>
       <c r="C3" t="str">
-        <v>Reichel</v>
+        <v>Schumm</v>
       </c>
       <c r="D3" t="str">
         <v>Male</v>
@@ -546,7 +546,7 @@
         <v>8976589760</v>
       </c>
       <c r="F3" t="str">
-        <v>Stanley_Ryan-Ortiz6@hotmail.com</v>
+        <v>Claude92@hotmail.com</v>
       </c>
       <c r="G3" t="str">
         <v>2003-02-09</v>
@@ -596,13 +596,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AMFH72</v>
+        <v>AFTF94</v>
       </c>
       <c r="B4" t="str">
-        <v>Eleanora</v>
+        <v>Solon</v>
       </c>
       <c r="C4" t="str">
-        <v>Muller</v>
+        <v>Berge</v>
       </c>
       <c r="D4" t="str">
         <v>Male</v>
@@ -611,7 +611,7 @@
         <v>8976589760</v>
       </c>
       <c r="F4" t="str">
-        <v>Mitchell53@hotmail.com</v>
+        <v>Ansel_Volkman7@yahoo.com</v>
       </c>
       <c r="G4" t="str">
         <v>2003-02-09</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AEBZ21</v>
+        <v>ASOL92</v>
       </c>
       <c r="B5" t="str">
-        <v>Walter</v>
+        <v>Akeem</v>
       </c>
       <c r="C5" t="str">
-        <v>Gutmann</v>
+        <v>Stroman</v>
       </c>
       <c r="D5" t="str">
         <v>Male</v>
@@ -676,7 +676,7 @@
         <v>8976589760</v>
       </c>
       <c r="F5" t="str">
-        <v>Ena_Murphy83@gmail.com</v>
+        <v>Nayeli.Carroll72@hotmail.com</v>
       </c>
       <c r="G5" t="str">
         <v>2003-02-09</v>
@@ -726,13 +726,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>APQV48</v>
+        <v>ABPR42</v>
       </c>
       <c r="B6" t="str">
-        <v>Irma</v>
+        <v>Roland</v>
       </c>
       <c r="C6" t="str">
-        <v>Okuneva</v>
+        <v>Kemmer</v>
       </c>
       <c r="D6" t="str">
         <v>Male</v>
@@ -741,7 +741,7 @@
         <v>8976589760</v>
       </c>
       <c r="F6" t="str">
-        <v>Bobbie_Gleichner68@gmail.com</v>
+        <v>Doreen_Bernhard@hotmail.com</v>
       </c>
       <c r="G6" t="str">
         <v>2003-02-09</v>

--- a/testdata/generated_employee_details.xlsx
+++ b/testdata/generated_employee_details.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AZLI45</v>
+        <v>ARVF24</v>
       </c>
       <c r="B2" t="str">
-        <v>Elsa</v>
+        <v>Christine</v>
       </c>
       <c r="C2" t="str">
-        <v>Crist</v>
+        <v>Schuppe</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,13 +481,13 @@
         <v>8976589760</v>
       </c>
       <c r="F2" t="str">
-        <v>Jeremiah_Auer1@gmail.com</v>
+        <v>Clara71@hotmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-27</v>
       </c>
       <c r="I2" t="str">
         <v>B.Tech</v>
@@ -531,13 +531,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AJRM91</v>
+        <v>AKGW92</v>
       </c>
       <c r="B3" t="str">
-        <v>Deshaun</v>
+        <v>Enos</v>
       </c>
       <c r="C3" t="str">
-        <v>Schumm</v>
+        <v>Kuhic</v>
       </c>
       <c r="D3" t="str">
         <v>Male</v>
@@ -546,13 +546,13 @@
         <v>8976589760</v>
       </c>
       <c r="F3" t="str">
-        <v>Claude92@hotmail.com</v>
+        <v>Jeremiah.Beier@hotmail.com</v>
       </c>
       <c r="G3" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-30</v>
       </c>
       <c r="I3" t="str">
         <v>B.Tech</v>
@@ -596,13 +596,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AFTF94</v>
+        <v>ASHL63</v>
       </c>
       <c r="B4" t="str">
-        <v>Solon</v>
+        <v>Leland</v>
       </c>
       <c r="C4" t="str">
-        <v>Berge</v>
+        <v>Goodwin</v>
       </c>
       <c r="D4" t="str">
         <v>Male</v>
@@ -611,13 +611,13 @@
         <v>8976589760</v>
       </c>
       <c r="F4" t="str">
-        <v>Ansel_Volkman7@yahoo.com</v>
+        <v>Loma_Nikolaus@hotmail.com</v>
       </c>
       <c r="G4" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-31</v>
       </c>
       <c r="I4" t="str">
         <v>B.Tech</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ASOL92</v>
+        <v>AEIK26</v>
       </c>
       <c r="B5" t="str">
-        <v>Akeem</v>
+        <v>Yasmin</v>
       </c>
       <c r="C5" t="str">
-        <v>Stroman</v>
+        <v>Cummerata</v>
       </c>
       <c r="D5" t="str">
         <v>Male</v>
@@ -676,13 +676,13 @@
         <v>8976589760</v>
       </c>
       <c r="F5" t="str">
-        <v>Nayeli.Carroll72@hotmail.com</v>
+        <v>Audrey63@yahoo.com</v>
       </c>
       <c r="G5" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-03-25</v>
+        <v>2026-04-01</v>
       </c>
       <c r="I5" t="str">
         <v>B.Tech</v>
@@ -726,13 +726,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ABPR42</v>
+        <v>AZPK39</v>
       </c>
       <c r="B6" t="str">
-        <v>Roland</v>
+        <v>Elisabeth</v>
       </c>
       <c r="C6" t="str">
-        <v>Kemmer</v>
+        <v>Legros</v>
       </c>
       <c r="D6" t="str">
         <v>Male</v>
@@ -741,13 +741,13 @@
         <v>8976589760</v>
       </c>
       <c r="F6" t="str">
-        <v>Doreen_Bernhard@hotmail.com</v>
+        <v>Era.Sipes95@yahoo.com</v>
       </c>
       <c r="G6" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-03-26</v>
+        <v>2026-04-02</v>
       </c>
       <c r="I6" t="str">
         <v>B.Tech</v>

--- a/testdata/generated_employee_details.xlsx
+++ b/testdata/generated_employee_details.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ARVF24</v>
+        <v>AOYF17</v>
       </c>
       <c r="B2" t="str">
-        <v>Christine</v>
+        <v>Jeffrey</v>
       </c>
       <c r="C2" t="str">
-        <v>Schuppe</v>
+        <v>Marquardt</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>8976589760</v>
       </c>
       <c r="F2" t="str">
-        <v>Clara71@hotmail.com</v>
+        <v>Peggy.Beahan@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>2003-02-09</v>
@@ -531,13 +531,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AKGW92</v>
+        <v>AHND28</v>
       </c>
       <c r="B3" t="str">
-        <v>Enos</v>
+        <v>Norma</v>
       </c>
       <c r="C3" t="str">
-        <v>Kuhic</v>
+        <v>Crona</v>
       </c>
       <c r="D3" t="str">
         <v>Male</v>
@@ -546,7 +546,7 @@
         <v>8976589760</v>
       </c>
       <c r="F3" t="str">
-        <v>Jeremiah.Beier@hotmail.com</v>
+        <v>Lila.Reynolds@gmail.com</v>
       </c>
       <c r="G3" t="str">
         <v>2003-02-09</v>
@@ -596,13 +596,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ASHL63</v>
+        <v>AHEX59</v>
       </c>
       <c r="B4" t="str">
-        <v>Leland</v>
+        <v>Annette</v>
       </c>
       <c r="C4" t="str">
-        <v>Goodwin</v>
+        <v>Quitzon</v>
       </c>
       <c r="D4" t="str">
         <v>Male</v>
@@ -611,7 +611,7 @@
         <v>8976589760</v>
       </c>
       <c r="F4" t="str">
-        <v>Loma_Nikolaus@hotmail.com</v>
+        <v>Amie3@hotmail.com</v>
       </c>
       <c r="G4" t="str">
         <v>2003-02-09</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AEIK26</v>
+        <v>ADLS40</v>
       </c>
       <c r="B5" t="str">
-        <v>Yasmin</v>
+        <v>Glenda</v>
       </c>
       <c r="C5" t="str">
-        <v>Cummerata</v>
+        <v>Cronin</v>
       </c>
       <c r="D5" t="str">
         <v>Male</v>
@@ -676,7 +676,7 @@
         <v>8976589760</v>
       </c>
       <c r="F5" t="str">
-        <v>Audrey63@yahoo.com</v>
+        <v>Matthew.Kuhic25@hotmail.com</v>
       </c>
       <c r="G5" t="str">
         <v>2003-02-09</v>
@@ -726,13 +726,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AZPK39</v>
+        <v>AFCY78</v>
       </c>
       <c r="B6" t="str">
-        <v>Elisabeth</v>
+        <v>Kaley</v>
       </c>
       <c r="C6" t="str">
-        <v>Legros</v>
+        <v>Ferry</v>
       </c>
       <c r="D6" t="str">
         <v>Male</v>
@@ -741,7 +741,7 @@
         <v>8976589760</v>
       </c>
       <c r="F6" t="str">
-        <v>Era.Sipes95@yahoo.com</v>
+        <v>Wm_Toy6@gmail.com</v>
       </c>
       <c r="G6" t="str">
         <v>2003-02-09</v>

--- a/testdata/generated_employee_details.xlsx
+++ b/testdata/generated_employee_details.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AOYF17</v>
+        <v>AJWO32</v>
       </c>
       <c r="B2" t="str">
-        <v>Jeffrey</v>
+        <v>Jackie</v>
       </c>
       <c r="C2" t="str">
-        <v>Marquardt</v>
+        <v>Wolff</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,13 +481,13 @@
         <v>8976589760</v>
       </c>
       <c r="F2" t="str">
-        <v>Peggy.Beahan@gmail.com</v>
+        <v>Matilde77@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-04-03</v>
       </c>
       <c r="I2" t="str">
         <v>B.Tech</v>
@@ -531,13 +531,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AHND28</v>
+        <v>AVYG36</v>
       </c>
       <c r="B3" t="str">
-        <v>Norma</v>
+        <v>Vickie</v>
       </c>
       <c r="C3" t="str">
-        <v>Crona</v>
+        <v>Gorczany</v>
       </c>
       <c r="D3" t="str">
         <v>Male</v>
@@ -546,13 +546,13 @@
         <v>8976589760</v>
       </c>
       <c r="F3" t="str">
-        <v>Lila.Reynolds@gmail.com</v>
+        <v>Daron.Cormier26@yahoo.com</v>
       </c>
       <c r="G3" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-03-30</v>
+        <v>2026-04-06</v>
       </c>
       <c r="I3" t="str">
         <v>B.Tech</v>
@@ -596,13 +596,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AHEX59</v>
+        <v>ASLT74</v>
       </c>
       <c r="B4" t="str">
-        <v>Annette</v>
+        <v>Tracy</v>
       </c>
       <c r="C4" t="str">
-        <v>Quitzon</v>
+        <v>OHaraTorp</v>
       </c>
       <c r="D4" t="str">
         <v>Male</v>
@@ -611,13 +611,13 @@
         <v>8976589760</v>
       </c>
       <c r="F4" t="str">
-        <v>Amie3@hotmail.com</v>
+        <v>Nina55@hotmail.com</v>
       </c>
       <c r="G4" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-03-31</v>
+        <v>2026-04-07</v>
       </c>
       <c r="I4" t="str">
         <v>B.Tech</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ADLS40</v>
+        <v>AUOG47</v>
       </c>
       <c r="B5" t="str">
-        <v>Glenda</v>
+        <v>Santiago</v>
       </c>
       <c r="C5" t="str">
-        <v>Cronin</v>
+        <v>Koelpin</v>
       </c>
       <c r="D5" t="str">
         <v>Male</v>
@@ -676,13 +676,13 @@
         <v>8976589760</v>
       </c>
       <c r="F5" t="str">
-        <v>Matthew.Kuhic25@hotmail.com</v>
+        <v>Johnathan43@yahoo.com</v>
       </c>
       <c r="G5" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-08</v>
       </c>
       <c r="I5" t="str">
         <v>B.Tech</v>
@@ -726,13 +726,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AFCY78</v>
+        <v>AJHF24</v>
       </c>
       <c r="B6" t="str">
-        <v>Kaley</v>
+        <v>Mark</v>
       </c>
       <c r="C6" t="str">
-        <v>Ferry</v>
+        <v>Pagac</v>
       </c>
       <c r="D6" t="str">
         <v>Male</v>
@@ -741,13 +741,13 @@
         <v>8976589760</v>
       </c>
       <c r="F6" t="str">
-        <v>Wm_Toy6@gmail.com</v>
+        <v>Crystal_Boyer66@gmail.com</v>
       </c>
       <c r="G6" t="str">
         <v>2003-02-09</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-09</v>
       </c>
       <c r="I6" t="str">
         <v>B.Tech</v>
